--- a/Quiz_Web_Matematika_Paket_1.xlsx
+++ b/Quiz_Web_Matematika_Paket_1.xlsx
@@ -436,19 +436,6 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -720,7 +707,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -744,8 +731,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>2</v>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -832,27 +821,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48 meter</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72 meter</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96 meter</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120 meter</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
-        <v>3</v>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -1081,7 +1068,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1105,8 +1092,10 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1241,27 +1230,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>08.30 WIB</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>09.00 WIB</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>09.15 WIB</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>09.30 WIB</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>2</v>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1393,7 +1380,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1417,8 +1404,10 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>3</v>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1500,27 +1489,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 32 kg dan Median = 34 kg</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 34 kg dan Median = 35 kg</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 32 kg dan Median = 35 kg</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Modus = 35 kg dan Median = 34 kg</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>

--- a/Quiz_Web_Matematika_Paket_1.xlsx
+++ b/Quiz_Web_Matematika_Paket_1.xlsx
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Adit berlatih renang setiap 4 hari sekali, Bayu setiap 6 hari sekali, dan Citra setiap 8 hari sekali. Pada hari Senin, 2 Maret 2026, mereka bertiga berlatih renang bersama untuk pertama kalinya. Pada hari dan tanggal berapakah mereka akan berlatih renang bersama untuk kedua kalinya?</t>
+          <t>Pak Budi memanen 48 buah mangga dan 72 buah jeruk. Buah-buah tersebut akan dimasukkan ke dalam keranjang dengan jumlah mangga dan jeruk yang sama di setiap keranjang tanpa ada sisa. Tentukan pernyataan berikut yang BENAR! (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,28 +712,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Rabu, 25 Maret 2026</t>
+          <t>FPB dari 48 dan 72 adalah 24, sehingga jumlah keranjang maksimal adalah 24.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kamis, 26 Maret 2026</t>
+          <t>Setiap keranjang berisi 2 buah mangga.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Jumat, 27 Maret 2026</t>
+          <t>Setiap keranjang berisi 4 buah jeruk.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sabtu, 28 Maret 2026</t>
+          <t>Total buah di setiap keranjang adalah 6 buah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 4</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
@@ -742,17 +742,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Cari KPK dari 4, 6, dan 8:
-   4 = 2²
-   6 = 2 × 3
-   8 = 2³
-   KPK = 2³ × 3 = 8 × 3 = 24 hari.
-2. Mereka akan bersama 24 hari setelah 2 Maret 2026:
-   Tanggal = 2 + 24 = 26 Maret 2026.
-3. Menentukan hari: 24 : 7 = 3 sisa 3 hari.
-   3 hari setelah Senin adalah Kamis (Senin -&gt; Selasa -&gt; Rabu -&gt; Kamis).
-Jadi, mereka berlatih bersama lagi pada hari Kamis, 26 Maret 2026 (Pilihan B).</t>
+          <t>FPB(48, 72) = 24. A: Benar, 24 keranjang. B: 48/24 = 2 mangga/keranjang, Benar. C: 72/24 = 3 jeruk/keranjang (bukan 4), SALAH. D: 2 + 3 = 5 buah total per keranjang (bukan 6), SALAH. Jawaban benar: A, B.</t>
         </is>
       </c>
     </row>
@@ -811,7 +801,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sebidang tanah aula pertemuan berbentuk persegi memiliki luas 576 m². Di sekeliling tanah aula tersebut akan dipasang kawat pagar pembatas sebanyak satu putaran penuh. Berapakah panjang kawat yang diperlukan untuk mengelilingi tanah tersebut?</t>
+          <t>Toko 'Buku Pintar' memberikan promosi: Buku A Rp50.000 diskon 20%, Buku B Rp40.000 diskon 1/4, Buku C Rp60.000 menjadi Rp45.000. Tentukan kebenaran pernyataan!</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -821,17 +811,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Potongan harga Buku A sebesar Rp10.000.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Harga yang dibayar untuk Buku B adalah Rp30.000.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Persentase diskon Buku C adalah 30%.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -847,12 +837,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Luas persegi = sisi × sisi = s²
-   s² = 576 m² -&gt; s = √576 = 24 meter.
-2. Keliling persegi = 4 × sisi
-   Keliling = 4 × 24 m = 96 meter.
-Jadi, kawat yang diperlukan adalah 96 meter (Pilihan C).</t>
+          <t>A: 20% × 50.000 = 10.000 (BENAR). B: 1/4 × 40.000 = 10.000 potongan, bayar = 30.000 (BENAR). C: Potongan = 15.000, persen = 15.000/60.000 × 100% = 25% (SALAH, bukan 30%).</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1048,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sebuah bidang hiasan dinding berbentuk gabungan persegi panjang dan segitiga sama kaki. Persegi panjang memiliki panjang 18 cm dan lebar 10 cm. Di atas salah satu sisi panjangnya menempel alas segitiga sama kaki yang berukuran alas 18 cm dan tinggi 8 cm. Berapakah luas total bangun gabungan tersebut?</t>
+          <t>Sebuah bangun datar memiliki ciri-ciri: (1) Memiliki 2 pasang sisi sejajar dan sama panjang, (2) Semua sudutnya sudut siku-siku, (3) Diagonalnya sama panjang dan saling membagi dua sama panjang. Pernyataan manakah yang BENAR mengenai bangun datar ini? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1073,22 +1058,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>216 cm²</t>
+          <t>Bangun tersebut adalah persegi panjang.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>252 cm²</t>
+          <t>Bangun tersebut adalah persegi.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>288 cm²</t>
+          <t>Luas bangun datar = panjang × lebar.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324 cm²</t>
+          <t>Keliling bangun datar = 4 × sisi.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1103,12 +1088,7 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Luas Persegi Panjang = panjang × lebar = 18 cm × 10 cm = 180 cm².
-2. Luas Segitiga = 1/2 × alas × tinggi = 1/2 × 18 cm × 8 cm = 9 × 8 = 72 cm².
-3. Luas Gabungan = Luas persegi panjang + Luas segitiga
-   Luas Total = 180 cm² + 72 cm² = 252 cm².
-Jadi, luas gabungan tersebut adalah 252 cm² (Pilihan B).</t>
+          <t>Ciri-ciri cocok dengan persegi panjang (bukan persegi karena tidak disebut sisi semua sama). A: Benar. B: SALAH, bisa persegi panjang biasa. C: Benar (luas persegi panjang). D: SALAH (keliling persegi, bukan persegi panjang). Jawaban benar: A, C.</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1200,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Pak Rahmat berangkat dari Bandung menuju Jakarta mengendarai mobil dengan kecepatan rata-rata 75 km/jam. Jarak yang ditempuh adalah 150 km. Jika Pak Rahmat berangkat dari Bandung pada pukul 06.30 WIB dan sempat beristirahat di rest area selama 30 menit di tengah perjalanan, pada pukul berapakah Pak Rahmat tiba di Jakarta?</t>
+          <t>Perhatikan jaring-jaring bangun ruang berikut! Tentukan kebenaran setiap pernyataan.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1230,17 +1210,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Jaring-jaring kubus terdiri dari 6 buah persegi yang kongruen.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Jaring-jaring tabung tanpa tutup terdiri dari 2 lingkaran dan 1 persegi panjang.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Jaring-jaring limas segiempat terdiri dari 1 persegi dan 4 segitiga.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1256,14 +1236,7 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Waktu tempuh murni = Jarak : Kecepatan
-   Waktu = 150 km : 75 km/jam = 2 jam.
-2. Waktu istirahat = 30 menit (0,5 jam).
-3. Total durasi perjalanan = 2 jam + 30 menit = 2 jam 30 menit.
-4. Waktu kedatangan = Waktu berangkat + Total durasi
-   = 06.30 WIB + 02.30 = 09.00 WIB.
-Jadi, Pak Rahmat tiba di Jakarta pada pukul 09.00 WIB (Pilihan B).</t>
+          <t>A: BENAR (kubus = 6 persegi kongruen). B: SALAH (tabung tanpa tutup = 1 lingkaran + 1 persegi panjang, BUKAN 2 lingkaran). C: BENAR (limas segiempat = 1 persegi alas + 4 segitiga sisi tegak).</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1348,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Data penjualan buku ensiklopedia anak di sebuah toko buku selama enam hari berturut-turut tercatat sebagai berikut: Senin 35 buku, Selasa 45 buku, Rabu 40 buku, Kamis 55 buku, Jumat 50 buku, dan Sabtu 75 buku. Berapakah rata-rata penjualan buku per hari selama enam hari tersebut?</t>
+          <t>Perpustakaan SD menyajikan data pengunjung menggunakan piktogram: 1 simbol buku besar = 20 pengunjung, 1 simbol buku kecil = 10 pengunjung. Data: Senin (3 besar + 1 kecil), Selasa (4 besar), Rabu (2 besar + 1 kecil). Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1385,28 +1358,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45 buku</t>
+          <t>Pengunjung hari Senin = 70 orang.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48 buku</t>
+          <t>Pengunjung hari Selasa = 80 orang.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50 buku</t>
+          <t>Total pengunjung 3 hari = 210 orang.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52 buku</t>
+          <t>Hari Rabu memiliki pengunjung paling sedikit.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 4</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1415,11 +1388,7 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Jumlah seluruh buku terjual = 35 + 45 + 40 + 55 + 50 + 75 = 300 buku.
-2. Banyaknya hari penjualan = 6 hari.
-3. Rata-rata per hari = 300 : 6 = 50 buku.
-Jadi, rata-rata penjualan buku per hari adalah 50 buku (Pilihan C).</t>
+          <t>Senin: 3×20 + 1×10 = 70 orang (A Benar). Selasa: 4×20 = 80 orang (B Benar). Rabu: 2×20 + 1×10 = 50 orang. Total 3 hari = 70+80+50 = 200 orang (C SALAH, bukan 210). Hari Rabu paling sedikit = 50 orang (D Benar). Jawaban benar: A, B, D.</t>
         </is>
       </c>
     </row>
@@ -1477,9 +1446,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Data berat badan (dalam kg) dari 15 siswa kelas VI SD disajikan sebagai berikut:
-32, 34, 32, 36, 35, 34, 32, 38, 35, 36, 32, 32, 35, 37, 34.
-Modus dan median dari data berat badan siswa tersebut berturut-turut adalah....</t>
+          <t>Perhatikan dua barisan bilangan! Barisan X: 3, 6, 12, 24, 48... Barisan Y: 5, 9, 13, 17, 21... Tentukan kebenaran pernyataan!</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1489,17 +1456,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Barisan X adalah barisan geometri dengan rasio 2.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Barisan Y adalah barisan aritmatika dengan beda 4.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Suku ke-6 Barisan X adalah 96.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1515,20 +1482,7 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Menentukan Modus (data paling sering muncul):
-   - 32 muncul sebanyak 5 kali
-   - 34 muncul sebanyak 3 kali
-   - 35 muncul sebanyak 3 kali
-   - 36 muncul sebanyak 2 kali
-   - 37 muncul sebanyak 1 kali
-   - 38 muncul sebanyak 1 kali
-   Modus = 32 kg.
-2. Menentukan Median (urutkan data dari terkecil):
-   32, 32, 32, 32, 32, 34, 34, [34], 35, 35, 35, 36, 36, 37, 38.
-   Data ke-8 (nilai tengah) adalah 34 kg.
-   Median = 34 kg.
-Jadi, modus = 32 kg dan median = 34 kg (Pilihan A).</t>
+          <t>A: 6/3=2, 12/6=2, 24/12=2 → Geometri rasio 2 (BENAR). B: 9-5=4, 13-9=4, 17-13=4 → Aritmatika beda 4 (BENAR). C: Suku ke-6 X = 48 × 2 = 96 (BENAR). Semua BENAR.</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Matematika_Paket_1.xlsx
+++ b/Quiz_Web_Matematika_Paket_1.xlsx
@@ -436,6 +436,19 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -702,39 +715,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Pak Budi memanen 48 buah mangga dan 72 buah jeruk. Buah-buah tersebut akan dimasukkan ke dalam keranjang dengan jumlah mangga dan jeruk yang sama di setiap keranjang tanpa ada sisa. Tentukan pernyataan berikut yang BENAR! (Pilih lebih dari satu)</t>
+          <t>Adit berlatih renang setiap 4 hari sekali, Bayu setiap 6 hari sekali, dan Citra setiap 8 hari sekali. Pada hari Senin, 2 Maret 2026, mereka bertiga berlatih renang bersama untuk pertama kalinya. Pada hari dan tanggal berapakah mereka akan berlatih renang bersama untuk kedua kalinya?</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FPB dari 48 dan 72 adalah 24, sehingga jumlah keranjang maksimal adalah 24.</t>
+          <t>Rabu, 25 Maret 2026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Setiap keranjang berisi 2 buah mangga.</t>
+          <t>Kamis, 26 Maret 2026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Setiap keranjang berisi 4 buah jeruk.</t>
+          <t>Jumat, 27 Maret 2026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Total buah di setiap keranjang adalah 6 buah.</t>
+          <t>Sabtu, 28 Maret 2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 4</t>
-        </is>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -742,7 +753,17 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>FPB(48, 72) = 24. A: Benar, 24 keranjang. B: 48/24 = 2 mangga/keranjang, Benar. C: 72/24 = 3 jeruk/keranjang (bukan 4), SALAH. D: 2 + 3 = 5 buah total per keranjang (bukan 6), SALAH. Jawaban benar: A, B.</t>
+          <t>Langkah penyelesaian:
+1. Cari KPK dari 4, 6, dan 8:
+   4 = 2²
+   6 = 2 × 3
+   8 = 2³
+   KPK = 2³ × 3 = 8 × 3 = 24 hari.
+2. Mereka akan bersama 24 hari setelah 2 Maret 2026:
+   Tanggal = 2 + 24 = 26 Maret 2026.
+3. Menentukan hari: 24 : 7 = 3 sisa 3 hari.
+   3 hari setelah Senin adalah Kamis (Senin -&gt; Selasa -&gt; Rabu -&gt; Kamis).
+Jadi, mereka berlatih bersama lagi pada hari Kamis, 26 Maret 2026 (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -801,7 +822,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Toko 'Buku Pintar' memberikan promosi: Buku A Rp50.000 diskon 20%, Buku B Rp40.000 diskon 1/4, Buku C Rp60.000 menjadi Rp45.000. Tentukan kebenaran pernyataan!</t>
+          <t>Sebidang tanah aula pertemuan berbentuk persegi memiliki luas 576 m². Di sekeliling tanah aula tersebut akan dipasang kawat pagar pembatas sebanyak satu putaran penuh. Berapakah panjang kawat yang diperlukan untuk mengelilingi tanah tersebut?</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -811,25 +832,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Potongan harga Buku A sebesar Rp10.000.</t>
+          <t>48 meter</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Harga yang dibayar untuk Buku B adalah Rp30.000.</t>
+          <t>72 meter</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Persentase diskon Buku C adalah 30%.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>96 meter</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>120 meter</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -837,7 +860,12 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>A: 20% × 50.000 = 10.000 (BENAR). B: 1/4 × 40.000 = 10.000 potongan, bayar = 30.000 (BENAR). C: Potongan = 15.000, persen = 15.000/60.000 × 100% = 25% (SALAH, bukan 30%).</t>
+          <t>Langkah penyelesaian:
+1. Luas persegi = sisi × sisi = s²
+   s² = 576 m² -&gt; s = √576 = 24 meter.
+2. Keliling persegi = 4 × sisi
+   Keliling = 4 × 24 m = 96 meter.
+Jadi, kawat yang diperlukan adalah 96 meter (Pilihan C).</t>
         </is>
       </c>
     </row>
@@ -1048,39 +1076,37 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sebuah bangun datar memiliki ciri-ciri: (1) Memiliki 2 pasang sisi sejajar dan sama panjang, (2) Semua sudutnya sudut siku-siku, (3) Diagonalnya sama panjang dan saling membagi dua sama panjang. Pernyataan manakah yang BENAR mengenai bangun datar ini? (Pilih lebih dari satu)</t>
+          <t>Sebuah bidang hiasan dinding berbentuk gabungan persegi panjang dan segitiga sama kaki. Persegi panjang memiliki panjang 18 cm dan lebar 10 cm. Di atas salah satu sisi panjangnya menempel alas segitiga sama kaki yang berukuran alas 18 cm dan tinggi 8 cm. Berapakah luas total bangun gabungan tersebut?</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Bangun tersebut adalah persegi panjang.</t>
+          <t>216 cm²</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bangun tersebut adalah persegi.</t>
+          <t>252 cm²</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Luas bangun datar = panjang × lebar.</t>
+          <t>288 cm²</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Keliling bangun datar = 4 × sisi.</t>
+          <t>324 cm²</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>1, 3</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1088,7 +1114,12 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Ciri-ciri cocok dengan persegi panjang (bukan persegi karena tidak disebut sisi semua sama). A: Benar. B: SALAH, bisa persegi panjang biasa. C: Benar (luas persegi panjang). D: SALAH (keliling persegi, bukan persegi panjang). Jawaban benar: A, C.</t>
+          <t>Langkah penyelesaian:
+1. Luas Persegi Panjang = panjang × lebar = 18 cm × 10 cm = 180 cm².
+2. Luas Segitiga = 1/2 × alas × tinggi = 1/2 × 18 cm × 8 cm = 9 × 8 = 72 cm².
+3. Luas Gabungan = Luas persegi panjang + Luas segitiga
+   Luas Total = 180 cm² + 72 cm² = 252 cm².
+Jadi, luas gabungan tersebut adalah 252 cm² (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1231,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Perhatikan jaring-jaring bangun ruang berikut! Tentukan kebenaran setiap pernyataan.</t>
+          <t>Pak Rahmat berangkat dari Bandung menuju Jakarta mengendarai mobil dengan kecepatan rata-rata 75 km/jam. Jarak yang ditempuh adalah 150 km. Jika Pak Rahmat berangkat dari Bandung pada pukul 06.30 WIB dan sempat beristirahat di rest area selama 30 menit di tengah perjalanan, pada pukul berapakah Pak Rahmat tiba di Jakarta?</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,25 +1241,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring kubus terdiri dari 6 buah persegi yang kongruen.</t>
+          <t>08.30 WIB</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring tabung tanpa tutup terdiri dari 2 lingkaran dan 1 persegi panjang.</t>
+          <t>09.00 WIB</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring limas segiempat terdiri dari 1 persegi dan 4 segitiga.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>09.15 WIB</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>09.30 WIB</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1236,7 +1269,14 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>A: BENAR (kubus = 6 persegi kongruen). B: SALAH (tabung tanpa tutup = 1 lingkaran + 1 persegi panjang, BUKAN 2 lingkaran). C: BENAR (limas segiempat = 1 persegi alas + 4 segitiga sisi tegak).</t>
+          <t>Langkah penyelesaian:
+1. Waktu tempuh murni = Jarak : Kecepatan
+   Waktu = 150 km : 75 km/jam = 2 jam.
+2. Waktu istirahat = 30 menit (0,5 jam).
+3. Total durasi perjalanan = 2 jam + 30 menit = 2 jam 30 menit.
+4. Waktu kedatangan = Waktu berangkat + Total durasi
+   = 06.30 WIB + 02.30 = 09.00 WIB.
+Jadi, Pak Rahmat tiba di Jakarta pada pukul 09.00 WIB (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1348,39 +1388,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Perpustakaan SD menyajikan data pengunjung menggunakan piktogram: 1 simbol buku besar = 20 pengunjung, 1 simbol buku kecil = 10 pengunjung. Data: Senin (3 besar + 1 kecil), Selasa (4 besar), Rabu (2 besar + 1 kecil). Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
+          <t>Data penjualan buku ensiklopedia anak di sebuah toko buku selama enam hari berturut-turut tercatat sebagai berikut: Senin 35 buku, Selasa 45 buku, Rabu 40 buku, Kamis 55 buku, Jumat 50 buku, dan Sabtu 75 buku. Berapakah rata-rata penjualan buku per hari selama enam hari tersebut?</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Pengunjung hari Senin = 70 orang.</t>
+          <t>45 buku</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pengunjung hari Selasa = 80 orang.</t>
+          <t>48 buku</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Total pengunjung 3 hari = 210 orang.</t>
+          <t>50 buku</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Hari Rabu memiliki pengunjung paling sedikit.</t>
+          <t>52 buku</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 4</t>
-        </is>
+      <c r="H19" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1388,7 +1426,11 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Senin: 3×20 + 1×10 = 70 orang (A Benar). Selasa: 4×20 = 80 orang (B Benar). Rabu: 2×20 + 1×10 = 50 orang. Total 3 hari = 70+80+50 = 200 orang (C SALAH, bukan 210). Hari Rabu paling sedikit = 50 orang (D Benar). Jawaban benar: A, B, D.</t>
+          <t>Langkah penyelesaian:
+1. Jumlah seluruh buku terjual = 35 + 45 + 40 + 55 + 50 + 75 = 300 buku.
+2. Banyaknya hari penjualan = 6 hari.
+3. Rata-rata per hari = 300 : 6 = 50 buku.
+Jadi, rata-rata penjualan buku per hari adalah 50 buku (Pilihan C).</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1488,9 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Perhatikan dua barisan bilangan! Barisan X: 3, 6, 12, 24, 48... Barisan Y: 5, 9, 13, 17, 21... Tentukan kebenaran pernyataan!</t>
+          <t>Data berat badan (dalam kg) dari 15 siswa kelas VI SD disajikan sebagai berikut:
+32, 34, 32, 36, 35, 34, 32, 38, 35, 36, 32, 32, 35, 37, 34.
+Modus dan median dari data berat badan siswa tersebut berturut-turut adalah....</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1456,25 +1500,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Barisan X adalah barisan geometri dengan rasio 2.</t>
+          <t>Modus = 32 kg dan Median = 34 kg</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Barisan Y adalah barisan aritmatika dengan beda 4.</t>
+          <t>Modus = 34 kg dan Median = 35 kg</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Suku ke-6 Barisan X adalah 96.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Modus = 32 kg dan Median = 35 kg</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Modus = 35 kg dan Median = 34 kg</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>
@@ -1482,7 +1528,20 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>A: 6/3=2, 12/6=2, 24/12=2 → Geometri rasio 2 (BENAR). B: 9-5=4, 13-9=4, 17-13=4 → Aritmatika beda 4 (BENAR). C: Suku ke-6 X = 48 × 2 = 96 (BENAR). Semua BENAR.</t>
+          <t>Langkah penyelesaian:
+1. Menentukan Modus (data paling sering muncul):
+   - 32 muncul sebanyak 5 kali
+   - 34 muncul sebanyak 3 kali
+   - 35 muncul sebanyak 3 kali
+   - 36 muncul sebanyak 2 kali
+   - 37 muncul sebanyak 1 kali
+   - 38 muncul sebanyak 1 kali
+   Modus = 32 kg.
+2. Menentukan Median (urutkan data dari terkecil):
+   32, 32, 32, 32, 32, 34, 34, [34], 35, 35, 35, 36, 36, 37, 38.
+   Data ke-8 (nilai tengah) adalah 34 kg.
+   Median = 34 kg.
+Jadi, modus = 32 kg dan median = 34 kg (Pilihan A).</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Matematika_Paket_1.xlsx
+++ b/Quiz_Web_Matematika_Paket_1.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,25 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F46E5"/>
-        <bgColor rgb="004F46E5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,117 +415,102 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Option 5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time in seconds</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Koperasi sekolah memiliki persediaan 35 pak buku tulis. Setiap pak berisi 10 buku tulis. Hari ini koperasi mendapat kiriman tambahan sebanyak 15 pak buku tulis yang masing-masing juga berisi 10 buku. Seluruh buku tulis tersebut akan dikemas ulang ke dalam 25 kardus dengan jumlah yang sama banyak untuk dibagikan ke kelas-kelas. Berapa banyak buku tulis dalam setiap kardus?</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>15 buku</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>20 buku</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>25 buku</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30 buku</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Total persediaan awal = 35 pak × 10 buku = 350 buku.
@@ -559,45 +523,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Suhu daging beku di dalam mesin pendingin (freezer) mula-mula adalah -12°C. Karena terjadi pemadaman listrik selama 40 menit, suhu di dalam mesin pendingin tersebut naik rata-rata 3°C setiap 8 menit. Berapakah suhu daging beku tersebut setelah listrik padam selama 40 menit?</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>-3°C</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0°C</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>3°C</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>6°C</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Lama pemadaman listrik = 40 menit.
@@ -609,45 +573,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Ibu Nani memiliki persediaan tepung terigu sebanyak 4 1/2 kg. Ibu menggunakannya untuk membuat kue bolu sebanyak 2 1/4 kg dan membuat donat sebanyak 1 1/8 kg. Berapa kilogram sisa tepung terigu Ibu Nani sekarang?</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1 1/8 kg</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1 1/4 kg</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1 3/8 kg</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1 1/2 kg</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Sisa tepung = 4 1/2 - 2 1/4 - 1 1/8
@@ -661,45 +615,43 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Perhatikan empat bilangan pecahan berikut: 0,65 ; 3/4 ; 60% ; 7/10. Urutan pecahan dari yang nilainya paling kecil ke paling besar adalah....</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>60% ; 0,65 ; 7/10 ; 3/4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>60% ; 7/10 ; 0,65 ; 3/4</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>0,65 ; 60% ; 3/4 ; 7/10</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>7/10 ; 60% ; 0,65 ; 3/4</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Langkah penyelesaian (ubah semua ke bentuk desimal):
 - 60% = 60/100 = 0,60
@@ -713,45 +665,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Adit berlatih renang setiap 4 hari sekali, Bayu setiap 6 hari sekali, dan Citra setiap 8 hari sekali. Pada hari Senin, 2 Maret 2026, mereka bertiga berlatih renang bersama untuk pertama kalinya. Pada hari dan tanggal berapakah mereka akan berlatih renang bersama untuk kedua kalinya?</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Rabu, 25 Maret 2026</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Kamis, 26 Maret 2026</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Jumat, 27 Maret 2026</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Sabtu, 28 Maret 2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Cari KPK dari 4, 6, dan 8:
@@ -768,45 +720,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Panitia bakti sosial sekolah menerima sumbangan berupa 72 kg beras, 48 bungkus minyak goreng, dan 36 kotak susu cair. Seluruh barang tersebut akan dikemas ke dalam beberapa paket bantuan dengan jenis dan jumlah barang yang sama banyak pada setiap paketnya tanpa ada yang tersisa. Berapa banyak paket bantuan terbanyak yang dapat dibuat oleh panitia?</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6 paket</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8 paket</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12 paket</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24 paket</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Jumlah paket terbanyak diperoleh dengan mencari FPB dari 72, 48, dan 36:
@@ -820,45 +762,43 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Sebidang tanah aula pertemuan berbentuk persegi memiliki luas 576 m². Di sekeliling tanah aula tersebut akan dipasang kawat pagar pembatas sebanyak satu putaran penuh. Berapakah panjang kawat yang diperlukan untuk mengelilingi tanah tersebut?</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>48 meter</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>72 meter</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>96 meter</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>120 meter</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Luas persegi = sisi × sisi = s²
@@ -870,45 +810,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Sebuah bak penampungan air berbentuk kubus mampu menampung air sampai penuh sebanyak 216.000 liter (dm³). Berapakah kedalaman (panjang rusuk bagian dalam) bak penampungan air tersebut dalam satuan meter?</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>4 meter</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>5 meter</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>6 meter</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>8 meter</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Volume kubus = s³
@@ -921,45 +861,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Perbandingan banyak siswa laki-laki dan siswa perempuan di kelas VI SD Harapan Bangsa adalah 4 : 5. Jika selisih banyak siswa laki-laki dan perempuan adalah 4 orang, berapakah jumlah seluruh siswa di kelas VI tersebut?</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>32 orang</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36 orang</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40 orang</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45 orang</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Rasio laki-laki : perempuan = 4 : 5.
@@ -973,45 +903,43 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Jarak antara Kota Melati dan Kota Cempaka pada sebuah peta adalah 6 cm. Skala yang tertera pada peta tersebut adalah 1 : 400.000. Berapakah jarak sebenarnya antara kedua kota tersebut dalam satuan kilometer?</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>18 km</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>24 km</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>28 km</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>32 km</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Jarak Sebenarnya = Jarak pada peta : Skala
@@ -1023,45 +951,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Sebuah taman rekreasi keluarga berbentuk lingkaran memiliki panjang jari-jari 14 meter (π = 22/7). Di sekeliling tepi taman tersebut akan ditanami pohon palem perindang dengan jarak antar-pohon sebesar 4 meter. Berapa banyak pohon palem yang dibutuhkan?</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>18 pohon</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>20 pohon</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>22 pohon</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>24 pohon</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Keliling lingkaran = 2 × π × r
@@ -1074,45 +1002,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Sebuah bidang hiasan dinding berbentuk gabungan persegi panjang dan segitiga sama kaki. Persegi panjang memiliki panjang 18 cm dan lebar 10 cm. Di atas salah satu sisi panjangnya menempel alas segitiga sama kaki yang berukuran alas 18 cm dan tinggi 8 cm. Berapakah luas total bangun gabungan tersebut?</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>216 cm²</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>252 cm²</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>288 cm²</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>324 cm²</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Luas Persegi Panjang = panjang × lebar = 18 cm × 10 cm = 180 cm².
@@ -1124,45 +1042,43 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Sebuah bak penampungan air berbentuk balok memiliki ukuran panjang 120 cm, lebar 80 cm, dan tinggi 100 cm. Bak tersebut telah terisi air sebanyak 3/4 bagian. Berapa liter air yang masih harus ditambahkan agar bak penampungan air tersebut terisi penuh?</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>180 liter</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>240 liter</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>320 liter</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>720 liter</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Volume total balok = p × l × t
@@ -1176,7 +1092,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Perhatikan ciri-ciri bangun ruang berikut:
 (1) Memiliki 5 buah sisi (1 sisi alas dan 4 sisi tegak berbentuk segitiga).
@@ -1185,40 +1101,40 @@
 Bangun ruang yang memiliki karakteristik tersebut adalah....</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Prisma segitiga</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Limas segitiga</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Limas segi empat</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Prisma segi empat</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Analisis sifat bangun ruang:
 - Prisma segitiga memiliki 5 sisi, 9 rusuk, 6 titik sudut.
@@ -1229,45 +1145,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Pak Rahmat berangkat dari Bandung menuju Jakarta mengendarai mobil dengan kecepatan rata-rata 75 km/jam. Jarak yang ditempuh adalah 150 km. Jika Pak Rahmat berangkat dari Bandung pada pukul 06.30 WIB dan sempat beristirahat di rest area selama 30 menit di tengah perjalanan, pada pukul berapakah Pak Rahmat tiba di Jakarta?</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>08.30 WIB</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>09.00 WIB</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>09.15 WIB</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>09.30 WIB</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Waktu tempuh murni = Jarak : Kecepatan
@@ -1281,45 +1187,43 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Sebuah kolam renang anak dengan kapasitas volume air 3.600 liter dikosongkan untuk dibersihkan menggunakan pipa pembuangan. Seluruh air di dalam kolam habis terkuras dalam waktu 30 menit. Berapakah debit aliran air yang keluar melalui pipa pembuangan tersebut dalam satuan liter/detik?</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>1,5 liter/detik</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2 liter/detik</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2,5 liter/detik</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>3 liter/detik</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Volume air = 3.600 liter.
@@ -1331,7 +1235,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Perhatikan tabel hasil panen jagung Desa Makmur berikut:
 - Tahun 2021: 45 ton
@@ -1342,40 +1246,40 @@
 Berapakah selisih hasil panen jagung tertinggi dan hasil panen jagung terendah selama periode tersebut?</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>20 ton</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>25 ton</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>30 ton</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>35 ton</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Hasil panen tertinggi terjadi pada tahun 2025 = 75 ton.
@@ -1386,45 +1290,35 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Data penjualan buku ensiklopedia anak di sebuah toko buku selama enam hari berturut-turut tercatat sebagai berikut: Senin 35 buku, Selasa 45 buku, Rabu 40 buku, Kamis 55 buku, Jumat 50 buku, dan Sabtu 75 buku. Berapakah rata-rata penjualan buku per hari selama enam hari tersebut?</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>45 buku</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>48 buku</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>50 buku</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52 buku</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Jumlah seluruh buku terjual = 35 + 45 + 40 + 55 + 50 + 75 = 300 buku.
@@ -1435,45 +1329,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Nilai ulangan matematika dari 8 orang siswa adalah: 75, 80, 85, 70, 90, 85, 75, dan 80. Ketika nilai ulangan milik siswa ke-9 dimasukkan ke dalam kelompok tersebut, nilai rata-rata keseluruhan menjadi 81. Berapakah nilai ulangan matematika siswa ke-9 tersebut?</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Jumlah nilai 8 siswa = 75 + 80 + 85 + 70 + 90 + 85 + 75 + 80 = 640.
@@ -1486,47 +1378,47 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Data berat badan (dalam kg) dari 15 siswa kelas VI SD disajikan sebagai berikut:
 32, 34, 32, 36, 35, 34, 32, 38, 35, 36, 32, 32, 35, 37, 34.
 Modus dan median dari data berat badan siswa tersebut berturut-turut adalah....</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Modus = 32 kg dan Median = 34 kg</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Modus = 34 kg dan Median = 35 kg</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Modus = 32 kg dan Median = 35 kg</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Modus = 35 kg dan Median = 34 kg</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Menentukan Modus (data paling sering muncul):
